--- a/data/to_test_function/input_test.xlsx
+++ b/data/to_test_function/input_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Desktop\OpenPeru\data\to_test_function\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F43467F-401D-4B79-849B-CCAE3DC13C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8B9E8B2-42DA-41C8-BD4D-1C7DDF3FDA6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{34264BE3-1B4E-47C2-8B79-C0289C72E04D}"/>
   </bookViews>
@@ -22,12 +22,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'L31989'!$A$4:$F$142</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2830" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2830" uniqueCount="598">
   <si>
     <t>id</t>
   </si>
@@ -1408,6 +1421,423 @@
   </si>
   <si>
     <t>13/03/2024</t>
+  </si>
+  <si>
+    <t>REYES CAM ABEL AUGUSTO</t>
+  </si>
+  <si>
+    <t>WONG PUJADA ENRIQUE</t>
+  </si>
+  <si>
+    <t>TUDELA GUTIERREZ ADRIANA JOSEFINA</t>
+  </si>
+  <si>
+    <t>AGUINAGA RECUENCO ALEJANDRO AURELIO</t>
+  </si>
+  <si>
+    <t>CAVERO ALVA ALEJANDRO ENRIQUE</t>
+  </si>
+  <si>
+    <t>MUNANTE BARRIOS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>SOTO REYES ALEJANDRO</t>
+  </si>
+  <si>
+    <t>PAREDES GONZALES ALEX ANTONIO</t>
+  </si>
+  <si>
+    <t>FLORES RAMIREZ ALEX RANDU</t>
+  </si>
+  <si>
+    <t>AZURIN LOAYZA ALFREDO</t>
+  </si>
+  <si>
+    <t>PARIONA SINCHE ALFREDO</t>
+  </si>
+  <si>
+    <t>GONZA CASTILLO AMERICO</t>
+  </si>
+  <si>
+    <t>ZEGARRA SABOYA ANA ZADITH</t>
+  </si>
+  <si>
+    <t>ORUE MEDINA ARIANA MAYBEE</t>
+  </si>
+  <si>
+    <t>ALEGRIA GARCIA ARTURO</t>
+  </si>
+  <si>
+    <t>OBANDO MORGAN AURISTELA ANA</t>
+  </si>
+  <si>
+    <t>QUITO SARMIENTO BERNARDO JAIME</t>
+  </si>
+  <si>
+    <t>ANDERSON RAMIREZ CARLOS ANTONIO</t>
+  </si>
+  <si>
+    <t>ALVA ROJAS CARLOS ENRIQUE</t>
+  </si>
+  <si>
+    <t>ZEBALLOS MADARIAGA CARLOS JAVIER</t>
+  </si>
+  <si>
+    <t>JUAREZ GALLEGOS CARMEN PATRICIA</t>
+  </si>
+  <si>
+    <t>REVILLA VILLANUEVA CESAR MANUEL</t>
+  </si>
+  <si>
+    <t>TRIGOZO REATEGUI CHERYL</t>
+  </si>
+  <si>
+    <t>ZETA CHUNGA CRUZ MARIA</t>
+  </si>
+  <si>
+    <t>JIMENEZ HEREDIA DAVID JULIO</t>
+  </si>
+  <si>
+    <t>GONZALES DELGADO DIANA CAROLINA</t>
+  </si>
+  <si>
+    <t>BAZAN CALDERON DIEGO ALONSO FERNANDO</t>
+  </si>
+  <si>
+    <t>CALLE LOBATON DIGNA</t>
+  </si>
+  <si>
+    <t>REYMUNDO MERCADO EDGARD CORNELIO</t>
+  </si>
+  <si>
+    <t>CASTILLO RIVAS EDUARDO ENRIQUE</t>
+  </si>
+  <si>
+    <t>SALHUANA CAVIDES EDUARDO</t>
+  </si>
+  <si>
+    <t>VARAS MELENDEZ ELIAS MARCIAL</t>
+  </si>
+  <si>
+    <t>MEDINA HERMOSILLA ELIZABETH SARA</t>
+  </si>
+  <si>
+    <t>JULON IRIGOIN ELVA EDHIT</t>
+  </si>
+  <si>
+    <t>VERGARA MENDOZA ELVIS HERNAN</t>
+  </si>
+  <si>
+    <t>BUSTAMANTE DONAYRE ERNESTO</t>
+  </si>
+  <si>
+    <t>MEDINA MINAYA ESDRAS RICARDO</t>
+  </si>
+  <si>
+    <t>ROSPIGLIOSI CAPURRO FERNANDO MIGUEL</t>
+  </si>
+  <si>
+    <t>CRUZ MAMANI FLAVIO</t>
+  </si>
+  <si>
+    <t>PABLO MEDINA FLOR AIDEE</t>
+  </si>
+  <si>
+    <t>PAREDES CASTRO FRANCIS JHASMINA</t>
+  </si>
+  <si>
+    <t>MALAGA TRILLO GEORGE EDWARD</t>
+  </si>
+  <si>
+    <t>TACURI VALDIVIA GERMAN ADOLFO</t>
+  </si>
+  <si>
+    <t>ECHAIZ RAMOS VDA DE NUNEZ GLADYS MARGOT</t>
+  </si>
+  <si>
+    <t>BELLIDO UGARTE GUIDO</t>
+  </si>
+  <si>
+    <t>BERMEJO ROJAS GUILLERMO</t>
+  </si>
+  <si>
+    <t>ECHEVERRIA RODRIGUEZ HAMLET</t>
+  </si>
+  <si>
+    <t>VENTURA ANGEL HECTOR JOSE</t>
+  </si>
+  <si>
+    <t>VALER PINTO HECTOR</t>
+  </si>
+  <si>
+    <t>JUAREZ CALLE HEIDY LISBETH</t>
+  </si>
+  <si>
+    <t>PORTERO LOPEZ HILDA MARLENY</t>
+  </si>
+  <si>
+    <t>GARCIA CORREA IDELSO MANUEL</t>
+  </si>
+  <si>
+    <t>LOPEZ URENA ILICH FREDY</t>
+  </si>
+  <si>
+    <t>MITA ALANOCA ISAAC</t>
+  </si>
+  <si>
+    <t>CORTEZ AGUIRRE ISABEL</t>
+  </si>
+  <si>
+    <t>RIVAS CHACARA JANET MILAGROS</t>
+  </si>
+  <si>
+    <t>PADILLA ROMERO JAVIER ROMMEL</t>
+  </si>
+  <si>
+    <t>LOPEZ MORALES JENY LUZ</t>
+  </si>
+  <si>
+    <t>ESPINOZA VARGAS JHAEC DARWIN</t>
+  </si>
+  <si>
+    <t>UGARTE MAMANI JHAKELINE KATY</t>
+  </si>
+  <si>
+    <t>MORANTE FIGARI JORGE ALBERTO</t>
+  </si>
+  <si>
+    <t>MARTICORENA MENDOZA JORGE ALFONSO</t>
+  </si>
+  <si>
+    <t>ZEBALLOS APONTE JORGE ARTURO</t>
+  </si>
+  <si>
+    <t>MONTOYA MANRIQUE JORGE CARLOS</t>
+  </si>
+  <si>
+    <t>FLORES ANCACHI JORGE LUIS</t>
+  </si>
+  <si>
+    <t>COAYLA JUAREZ JORGE SAMUEL</t>
+  </si>
+  <si>
+    <t>ARRIOLA TUEROS JOSE ALBERTO</t>
+  </si>
+  <si>
+    <t>PAZO NUNURA JOSE BERNARDO</t>
+  </si>
+  <si>
+    <t>WILLIAMS ZAPATA JOSE DANIEL</t>
+  </si>
+  <si>
+    <t>JERI ORE JOSE ENRIQUE</t>
+  </si>
+  <si>
+    <t>CUETO ASERVI JOSE ERNESTO</t>
+  </si>
+  <si>
+    <t>LUNA GALVEZ JOSE LEON</t>
+  </si>
+  <si>
+    <t>ELIAS AVALOS JOSE LUIS</t>
+  </si>
+  <si>
+    <t>BALCAZAR ZELADA JOSE MARIA</t>
+  </si>
+  <si>
+    <t>BURGOS OLIVEROS JUAN BARTOLOME</t>
+  </si>
+  <si>
+    <t>LIZARZABURU LIZARZABURU JUAN CARLOS MARTIN</t>
+  </si>
+  <si>
+    <t>MORI CELIS JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>PAREDES FONSECA KAROL IVETT</t>
+  </si>
+  <si>
+    <t>PORTALATINO AVALOS KELLY ROXANA</t>
+  </si>
+  <si>
+    <t>CAMONES SORIANO LADY MERCEDES</t>
+  </si>
+  <si>
+    <t>VASQUEZ VELA LUCINDA</t>
+  </si>
+  <si>
+    <t>ARAGON CARRENO LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>CORDERO JON TAY LUIS GUSTAVO</t>
+  </si>
+  <si>
+    <t>PICON QUEDO LUIS RAUL</t>
+  </si>
+  <si>
+    <t>KAMICHE MORANTE LUIS ROBERTO</t>
+  </si>
+  <si>
+    <t>SANTISTEBAN SUCLUPE MAGALLY</t>
+  </si>
+  <si>
+    <t>RUIZ RODRIGUEZ MAGALY ROSMERY</t>
+  </si>
+  <si>
+    <t>PALACIOS HUAMAN MARGOT</t>
+  </si>
+  <si>
+    <t>AGUERO GUTIERREZ MARIA ANTONIETA</t>
+  </si>
+  <si>
+    <t>JAUREGUI MARTINEZ DE AGUAYO MARIA DE LOS MILAGROS JACKELINE</t>
+  </si>
+  <si>
+    <t>ALVA PRIETO MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>TAIPE CORONADO MARIA ELIZABETH</t>
+  </si>
+  <si>
+    <t>ACUNA PERALTA MARIA GRIMANEZA</t>
+  </si>
+  <si>
+    <t>CORDOVA LOBATON MARIA JESSICA</t>
+  </si>
+  <si>
+    <t>MOYANO DELGADO MARTHA LUPE</t>
+  </si>
+  <si>
+    <t>INFANTES CASTANEDA MERY ELIANA</t>
+  </si>
+  <si>
+    <t>CICCIA VASQUEZ MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>HEIDINGER BALLESTEROS NELCY LIDIA</t>
+  </si>
+  <si>
+    <t>LIMACHI QUISPE NIEVES ESMERALDA</t>
+  </si>
+  <si>
+    <t>CHACON TRUJILLO NILZA MERLY</t>
+  </si>
+  <si>
+    <t>TELLO MONTES NIVARDO EDGAR</t>
+  </si>
+  <si>
+    <t>HERRERA MEDINA NOELIA ROSSVITH</t>
+  </si>
+  <si>
+    <t>YARROW LUMBRERAS NORMA MARTINA</t>
+  </si>
+  <si>
+    <t>ZEA CHOQUECHAMBI OSCAR</t>
+  </si>
+  <si>
+    <t>DAVILA ATANACIO PASION NEOMIAS</t>
+  </si>
+  <si>
+    <t>CHIRINOS VENEGAS PATRICIA ROSA</t>
+  </si>
+  <si>
+    <t>GUTIERREZ TICONA PAUL SILVIO</t>
+  </si>
+  <si>
+    <t>MARTINEZ TALAVERA PEDRO EDWIN</t>
+  </si>
+  <si>
+    <t>DOROTEO CARBAJO RAUL FELIPE</t>
+  </si>
+  <si>
+    <t>HUAMAN CORONADO RAUL</t>
+  </si>
+  <si>
+    <t>CHIABRA LEON ROBERTO ENRIQUE</t>
+  </si>
+  <si>
+    <t>SANCHEZ PALOMINO ROBERTO HELBERT</t>
+  </si>
+  <si>
+    <t>BARBARAN REYES ROSANGELLA ANDREA</t>
+  </si>
+  <si>
+    <t>TORRES SALINAS ROSIO</t>
+  </si>
+  <si>
+    <t>LUQUE IBARRA RUTH</t>
+  </si>
+  <si>
+    <t>ACUNA PERALTA SEGUNDO HECTOR</t>
+  </si>
+  <si>
+    <t>QUIROZ BARBOZA SEGUNDO TEODOMIRO</t>
+  </si>
+  <si>
+    <t>MONTALVO CUBAS SEGUNDO TORIBIO</t>
+  </si>
+  <si>
+    <t>BAZAN NARRO SIGRID TESORO</t>
+  </si>
+  <si>
+    <t>ROBLES ARAUJO SILVANA EMPERATRIZ</t>
+  </si>
+  <si>
+    <t>MONTEZA FACHO SILVIA MARIA</t>
+  </si>
+  <si>
+    <t>PAREDES PIQUE SUSEL ANA MARIA</t>
+  </si>
+  <si>
+    <t>RAMIREZ GARCIA TANIA ESTEFANY</t>
+  </si>
+  <si>
+    <t>CUTIPA CCAMA VICTOR RAUL</t>
+  </si>
+  <si>
+    <t>FLORES RUIZ VICTOR SEFERINO</t>
+  </si>
+  <si>
+    <t>OLIVOS MARTINEZ VIVIAN</t>
+  </si>
+  <si>
+    <t>CERRON ROJAS WALDEMAR JOSE</t>
+  </si>
+  <si>
+    <t>QUISPE MAMANI WILSON RUSBEL</t>
+  </si>
+  <si>
+    <t>SOTO PALACIOS WILSON</t>
+  </si>
+  <si>
+    <t>AMURUZ DULANTO YESSICA ROSSELLI</t>
+  </si>
+  <si>
+    <t>ALCARRAZ AGUERO YOREL KIRA</t>
+  </si>
+  <si>
+    <t>CHAVEZ CHINO BETSSY BETZABET</t>
+  </si>
+  <si>
+    <t>CORDERO JON TAY MARIA DEL PILAR</t>
+  </si>
+  <si>
+    <t>DIAZ MONAGO FREDDY RONALD</t>
+  </si>
+  <si>
+    <t>ELERA GARCIA WILMAR ALBERTO</t>
+  </si>
+  <si>
+    <t>GUERRA GARCIA CAMPOS HERNANDO</t>
+  </si>
+  <si>
+    <t>HERRERA MAMANI FERNANDO MARIO</t>
+  </si>
+  <si>
+    <t>SAAVEDRA CASTERNOQUE HITLER</t>
+  </si>
+  <si>
+    <t>voto</t>
   </si>
 </sst>
 </file>
@@ -5191,7 +5621,7 @@
         <v>4</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>5</v>
+        <v>597</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -5205,7 +5635,7 @@
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>459</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>9</v>
@@ -5225,7 +5655,7 @@
         <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>461</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>14</v>
@@ -5245,7 +5675,7 @@
         <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>462</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>19</v>
@@ -5265,7 +5695,7 @@
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>463</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>14</v>
@@ -5285,7 +5715,7 @@
         <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>464</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>26</v>
@@ -5305,7 +5735,7 @@
         <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>465</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>29</v>
@@ -5325,7 +5755,7 @@
         <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>466</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>33</v>
@@ -5345,7 +5775,7 @@
         <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>467</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>37</v>
@@ -5365,7 +5795,7 @@
         <v>39</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
+        <v>468</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>41</v>
@@ -5385,7 +5815,7 @@
         <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>469</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>37</v>
@@ -5405,7 +5835,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>470</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>9</v>
@@ -5425,7 +5855,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>50</v>
+        <v>471</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>41</v>
@@ -5445,7 +5875,7 @@
         <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>53</v>
+        <v>472</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>54</v>
@@ -5465,7 +5895,7 @@
         <v>57</v>
       </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>473</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>19</v>
@@ -5485,7 +5915,7 @@
         <v>60</v>
       </c>
       <c r="D19" t="s">
-        <v>61</v>
+        <v>474</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>19</v>
@@ -5505,7 +5935,7 @@
         <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>64</v>
+        <v>475</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>37</v>
@@ -5525,7 +5955,7 @@
         <v>66</v>
       </c>
       <c r="D21" t="s">
-        <v>67</v>
+        <v>476</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>68</v>
@@ -5545,7 +5975,7 @@
         <v>70</v>
       </c>
       <c r="D22" t="s">
-        <v>71</v>
+        <v>477</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>72</v>
@@ -5565,7 +5995,7 @@
         <v>74</v>
       </c>
       <c r="D23" t="s">
-        <v>75</v>
+        <v>478</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>76</v>
@@ -5585,7 +6015,7 @@
         <v>78</v>
       </c>
       <c r="D24" t="s">
-        <v>79</v>
+        <v>479</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>19</v>
@@ -5605,7 +6035,7 @@
         <v>81</v>
       </c>
       <c r="D25" t="s">
-        <v>82</v>
+        <v>480</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>19</v>
@@ -5625,7 +6055,7 @@
         <v>84</v>
       </c>
       <c r="D26" t="s">
-        <v>85</v>
+        <v>481</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>26</v>
@@ -5645,7 +6075,7 @@
         <v>87</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>482</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>19</v>
@@ -5665,7 +6095,7 @@
         <v>90</v>
       </c>
       <c r="D28" t="s">
-        <v>91</v>
+        <v>483</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>19</v>
@@ -5685,7 +6115,7 @@
         <v>93</v>
       </c>
       <c r="D29" t="s">
-        <v>94</v>
+        <v>484</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>14</v>
@@ -5705,7 +6135,7 @@
         <v>96</v>
       </c>
       <c r="D30" t="s">
-        <v>97</v>
+        <v>485</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>26</v>
@@ -5725,7 +6155,7 @@
         <v>99</v>
       </c>
       <c r="D31" t="s">
-        <v>100</v>
+        <v>486</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>54</v>
@@ -5745,7 +6175,7 @@
         <v>102</v>
       </c>
       <c r="D32" t="s">
-        <v>103</v>
+        <v>487</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>76</v>
@@ -5765,7 +6195,7 @@
         <v>105</v>
       </c>
       <c r="D33" t="s">
-        <v>106</v>
+        <v>488</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>19</v>
@@ -5785,7 +6215,7 @@
         <v>108</v>
       </c>
       <c r="D34" t="s">
-        <v>109</v>
+        <v>489</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>29</v>
@@ -5805,7 +6235,7 @@
         <v>111</v>
       </c>
       <c r="D35" t="s">
-        <v>112</v>
+        <v>490</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>113</v>
@@ -5825,7 +6255,7 @@
         <v>115</v>
       </c>
       <c r="D36" t="s">
-        <v>116</v>
+        <v>491</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>33</v>
@@ -5845,7 +6275,7 @@
         <v>118</v>
       </c>
       <c r="D37" t="s">
-        <v>119</v>
+        <v>492</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>29</v>
@@ -5865,7 +6295,7 @@
         <v>121</v>
       </c>
       <c r="D38" t="s">
-        <v>122</v>
+        <v>493</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>72</v>
@@ -5885,7 +6315,7 @@
         <v>124</v>
       </c>
       <c r="D39" t="s">
-        <v>125</v>
+        <v>494</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>19</v>
@@ -5905,7 +6335,7 @@
         <v>127</v>
       </c>
       <c r="D40" t="s">
-        <v>128</v>
+        <v>495</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>26</v>
@@ -5925,7 +6355,7 @@
         <v>130</v>
       </c>
       <c r="D41" t="s">
-        <v>131</v>
+        <v>496</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>19</v>
@@ -5945,7 +6375,7 @@
         <v>133</v>
       </c>
       <c r="D42" t="s">
-        <v>134</v>
+        <v>497</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>9</v>
@@ -5965,7 +6395,7 @@
         <v>136</v>
       </c>
       <c r="D43" t="s">
-        <v>137</v>
+        <v>498</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>68</v>
@@ -5985,7 +6415,7 @@
         <v>139</v>
       </c>
       <c r="D44" t="s">
-        <v>140</v>
+        <v>499</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>54</v>
@@ -6005,7 +6435,7 @@
         <v>142</v>
       </c>
       <c r="D45" t="s">
-        <v>143</v>
+        <v>500</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>68</v>
@@ -6025,7 +6455,7 @@
         <v>145</v>
       </c>
       <c r="D46" t="s">
-        <v>146</v>
+        <v>501</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>33</v>
@@ -6045,7 +6475,7 @@
         <v>149</v>
       </c>
       <c r="D47" t="s">
-        <v>150</v>
+        <v>502</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>151</v>
@@ -6065,7 +6495,7 @@
         <v>153</v>
       </c>
       <c r="D48" t="s">
-        <v>154</v>
+        <v>503</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>54</v>
@@ -6085,7 +6515,7 @@
         <v>156</v>
       </c>
       <c r="D49" t="s">
-        <v>157</v>
+        <v>504</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>113</v>
@@ -6105,7 +6535,7 @@
         <v>159</v>
       </c>
       <c r="D50" t="s">
-        <v>160</v>
+        <v>505</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>113</v>
@@ -6125,7 +6555,7 @@
         <v>162</v>
       </c>
       <c r="D51" t="s">
-        <v>163</v>
+        <v>506</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>19</v>
@@ -6145,7 +6575,7 @@
         <v>165</v>
       </c>
       <c r="D52" t="s">
-        <v>166</v>
+        <v>507</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>41</v>
@@ -6165,7 +6595,7 @@
         <v>168</v>
       </c>
       <c r="D53" t="s">
-        <v>169</v>
+        <v>508</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>54</v>
@@ -6185,7 +6615,7 @@
         <v>171</v>
       </c>
       <c r="D54" t="s">
-        <v>172</v>
+        <v>509</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>72</v>
@@ -6205,7 +6635,7 @@
         <v>174</v>
       </c>
       <c r="D55" t="s">
-        <v>175</v>
+        <v>510</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>29</v>
@@ -6225,7 +6655,7 @@
         <v>177</v>
       </c>
       <c r="D56" t="s">
-        <v>178</v>
+        <v>511</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>72</v>
@@ -6245,7 +6675,7 @@
         <v>180</v>
       </c>
       <c r="D57" t="s">
-        <v>181</v>
+        <v>512</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>9</v>
@@ -6265,7 +6695,7 @@
         <v>183</v>
       </c>
       <c r="D58" t="s">
-        <v>184</v>
+        <v>513</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>54</v>
@@ -6285,7 +6715,7 @@
         <v>186</v>
       </c>
       <c r="D59" t="s">
-        <v>187</v>
+        <v>514</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>9</v>
@@ -6305,7 +6735,7 @@
         <v>189</v>
       </c>
       <c r="D60" t="s">
-        <v>190</v>
+        <v>515</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>151</v>
@@ -6325,7 +6755,7 @@
         <v>192</v>
       </c>
       <c r="D61" t="s">
-        <v>193</v>
+        <v>516</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>19</v>
@@ -6345,7 +6775,7 @@
         <v>195</v>
       </c>
       <c r="D62" t="s">
-        <v>196</v>
+        <v>517</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>54</v>
@@ -6365,7 +6795,7 @@
         <v>198</v>
       </c>
       <c r="D63" t="s">
-        <v>199</v>
+        <v>518</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>33</v>
@@ -6385,7 +6815,7 @@
         <v>201</v>
       </c>
       <c r="D64" t="s">
-        <v>202</v>
+        <v>519</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>41</v>
@@ -6405,7 +6835,7 @@
         <v>204</v>
       </c>
       <c r="D65" t="s">
-        <v>205</v>
+        <v>520</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>29</v>
@@ -6425,7 +6855,7 @@
         <v>207</v>
       </c>
       <c r="D66" t="s">
-        <v>208</v>
+        <v>521</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>26</v>
@@ -6445,7 +6875,7 @@
         <v>210</v>
       </c>
       <c r="D67" t="s">
-        <v>211</v>
+        <v>522</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>151</v>
@@ -6465,7 +6895,7 @@
         <v>213</v>
       </c>
       <c r="D68" t="s">
-        <v>214</v>
+        <v>523</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>54</v>
@@ -6485,7 +6915,7 @@
         <v>216</v>
       </c>
       <c r="D69" t="s">
-        <v>217</v>
+        <v>524</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>113</v>
@@ -6505,7 +6935,7 @@
         <v>219</v>
       </c>
       <c r="D70" t="s">
-        <v>220</v>
+        <v>525</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>54</v>
@@ -6525,7 +6955,7 @@
         <v>222</v>
       </c>
       <c r="D71" t="s">
-        <v>223</v>
+        <v>526</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>41</v>
@@ -6545,7 +6975,7 @@
         <v>225</v>
       </c>
       <c r="D72" t="s">
-        <v>226</v>
+        <v>527</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>14</v>
@@ -6566,7 +6996,7 @@
         <v>228</v>
       </c>
       <c r="D73" t="s">
-        <v>229</v>
+        <v>528</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>41</v>
@@ -6586,7 +7016,7 @@
         <v>231</v>
       </c>
       <c r="D74" t="s">
-        <v>232</v>
+        <v>529</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>151</v>
@@ -6606,7 +7036,7 @@
         <v>234</v>
       </c>
       <c r="D75" t="s">
-        <v>235</v>
+        <v>530</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>54</v>
@@ -6626,7 +7056,7 @@
         <v>237</v>
       </c>
       <c r="D76" t="s">
-        <v>238</v>
+        <v>531</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>29</v>
@@ -6646,7 +7076,7 @@
         <v>240</v>
       </c>
       <c r="D77" t="s">
-        <v>241</v>
+        <v>532</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>9</v>
@@ -6666,7 +7096,7 @@
         <v>243</v>
       </c>
       <c r="D78" t="s">
-        <v>244</v>
+        <v>533</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>54</v>
@@ -6686,7 +7116,7 @@
         <v>246</v>
       </c>
       <c r="D79" t="s">
-        <v>247</v>
+        <v>534</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>29</v>
@@ -6706,7 +7136,7 @@
         <v>249</v>
       </c>
       <c r="D80" t="s">
-        <v>250</v>
+        <v>535</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>72</v>
@@ -6726,7 +7156,7 @@
         <v>252</v>
       </c>
       <c r="D81" t="s">
-        <v>253</v>
+        <v>536</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>14</v>
@@ -6746,7 +7176,7 @@
         <v>255</v>
       </c>
       <c r="D82" t="s">
-        <v>256</v>
+        <v>537</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>9</v>
@@ -6766,7 +7196,7 @@
         <v>258</v>
       </c>
       <c r="D83" t="s">
-        <v>259</v>
+        <v>538</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>29</v>
@@ -6786,7 +7216,7 @@
         <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>262</v>
+        <v>539</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>33</v>
@@ -6806,7 +7236,7 @@
         <v>264</v>
       </c>
       <c r="D85" t="s">
-        <v>265</v>
+        <v>540</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>72</v>
@@ -6826,7 +7256,7 @@
         <v>267</v>
       </c>
       <c r="D86" t="s">
-        <v>268</v>
+        <v>541</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>41</v>
@@ -6846,7 +7276,7 @@
         <v>270</v>
       </c>
       <c r="D87" t="s">
-        <v>271</v>
+        <v>542</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>54</v>
@@ -6866,7 +7296,7 @@
         <v>273</v>
       </c>
       <c r="D88" t="s">
-        <v>274</v>
+        <v>543</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>29</v>
@@ -6886,7 +7316,7 @@
         <v>276</v>
       </c>
       <c r="D89" t="s">
-        <v>277</v>
+        <v>544</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>19</v>
@@ -6906,7 +7336,7 @@
         <v>279</v>
       </c>
       <c r="D90" t="s">
-        <v>280</v>
+        <v>545</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>29</v>
@@ -6926,7 +7356,7 @@
         <v>282</v>
       </c>
       <c r="D91" t="s">
-        <v>283</v>
+        <v>546</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>68</v>
@@ -6946,7 +7376,7 @@
         <v>285</v>
       </c>
       <c r="D92" t="s">
-        <v>286</v>
+        <v>547</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>9</v>
@@ -6966,7 +7396,7 @@
         <v>288</v>
       </c>
       <c r="D93" t="s">
-        <v>289</v>
+        <v>548</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>26</v>
@@ -6986,7 +7416,7 @@
         <v>291</v>
       </c>
       <c r="D94" t="s">
-        <v>292</v>
+        <v>549</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>72</v>
@@ -7006,7 +7436,7 @@
         <v>294</v>
       </c>
       <c r="D95" t="s">
-        <v>295</v>
+        <v>550</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>9</v>
@@ -7026,7 +7456,7 @@
         <v>297</v>
       </c>
       <c r="D96" t="s">
-        <v>298</v>
+        <v>551</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>29</v>
@@ -7046,7 +7476,7 @@
         <v>300</v>
       </c>
       <c r="D97" t="s">
-        <v>301</v>
+        <v>552</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>26</v>
@@ -7066,7 +7496,7 @@
         <v>303</v>
       </c>
       <c r="D98" t="s">
-        <v>304</v>
+        <v>553</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>19</v>
@@ -7086,7 +7516,7 @@
         <v>306</v>
       </c>
       <c r="D99" t="s">
-        <v>307</v>
+        <v>554</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>19</v>
@@ -7106,7 +7536,7 @@
         <v>309</v>
       </c>
       <c r="D100" t="s">
-        <v>310</v>
+        <v>555</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>26</v>
@@ -7126,7 +7556,7 @@
         <v>312</v>
       </c>
       <c r="D101" t="s">
-        <v>313</v>
+        <v>556</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>29</v>
@@ -7146,7 +7576,7 @@
         <v>315</v>
       </c>
       <c r="D102" t="s">
-        <v>316</v>
+        <v>557</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>113</v>
@@ -7166,7 +7596,7 @@
         <v>318</v>
       </c>
       <c r="D103" t="s">
-        <v>319</v>
+        <v>558</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>19</v>
@@ -7186,7 +7616,7 @@
         <v>321</v>
       </c>
       <c r="D104" t="s">
-        <v>322</v>
+        <v>559</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>54</v>
@@ -7206,7 +7636,7 @@
         <v>324</v>
       </c>
       <c r="D105" t="s">
-        <v>325</v>
+        <v>560</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>26</v>
@@ -7226,7 +7656,7 @@
         <v>327</v>
       </c>
       <c r="D106" t="s">
-        <v>328</v>
+        <v>561</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>26</v>
@@ -7247,7 +7677,7 @@
         <v>330</v>
       </c>
       <c r="D107" t="s">
-        <v>331</v>
+        <v>562</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>33</v>
@@ -7267,7 +7697,7 @@
         <v>333</v>
       </c>
       <c r="D108" t="s">
-        <v>334</v>
+        <v>563</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>37</v>
@@ -7287,7 +7717,7 @@
         <v>336</v>
       </c>
       <c r="D109" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>26</v>
@@ -7307,7 +7737,7 @@
         <v>339</v>
       </c>
       <c r="D110" t="s">
-        <v>340</v>
+        <v>565</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>33</v>
@@ -7327,7 +7757,7 @@
         <v>342</v>
       </c>
       <c r="D111" t="s">
-        <v>343</v>
+        <v>566</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>68</v>
@@ -7347,7 +7777,7 @@
         <v>345</v>
       </c>
       <c r="D112" t="s">
-        <v>346</v>
+        <v>567</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>72</v>
@@ -7367,7 +7797,7 @@
         <v>348</v>
       </c>
       <c r="D113" t="s">
-        <v>349</v>
+        <v>568</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>19</v>
@@ -7387,7 +7817,7 @@
         <v>351</v>
       </c>
       <c r="D114" t="s">
-        <v>352</v>
+        <v>569</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>29</v>
@@ -7407,7 +7837,7 @@
         <v>354</v>
       </c>
       <c r="D115" t="s">
-        <v>355</v>
+        <v>570</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>113</v>
@@ -7427,7 +7857,7 @@
         <v>357</v>
       </c>
       <c r="D116" t="s">
-        <v>358</v>
+        <v>571</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>19</v>
@@ -7447,7 +7877,7 @@
         <v>360</v>
       </c>
       <c r="D117" t="s">
-        <v>361</v>
+        <v>572</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>29</v>
@@ -7467,7 +7897,7 @@
         <v>363</v>
       </c>
       <c r="D118" t="s">
-        <v>364</v>
+        <v>573</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>76</v>
@@ -7487,7 +7917,7 @@
         <v>297</v>
       </c>
       <c r="D119" t="s">
-        <v>366</v>
+        <v>574</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>68</v>
@@ -7507,7 +7937,7 @@
         <v>368</v>
       </c>
       <c r="D120" t="s">
-        <v>369</v>
+        <v>575</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>33</v>
@@ -7527,7 +7957,7 @@
         <v>371</v>
       </c>
       <c r="D121" t="s">
-        <v>372</v>
+        <v>576</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>9</v>
@@ -7547,7 +7977,7 @@
         <v>374</v>
       </c>
       <c r="D122" t="s">
-        <v>375</v>
+        <v>577</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>76</v>
@@ -7567,7 +7997,7 @@
         <v>377</v>
       </c>
       <c r="D123" t="s">
-        <v>378</v>
+        <v>578</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>37</v>
@@ -7587,7 +8017,7 @@
         <v>380</v>
       </c>
       <c r="D124" t="s">
-        <v>381</v>
+        <v>579</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>72</v>
@@ -7607,7 +8037,7 @@
         <v>383</v>
       </c>
       <c r="D125" t="s">
-        <v>384</v>
+        <v>580</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>76</v>
@@ -7627,7 +8057,7 @@
         <v>386</v>
       </c>
       <c r="D126" t="s">
-        <v>387</v>
+        <v>581</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>19</v>
@@ -7647,7 +8077,7 @@
         <v>389</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>582</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>113</v>
@@ -7667,7 +8097,7 @@
         <v>392</v>
       </c>
       <c r="D128" t="s">
-        <v>393</v>
+        <v>583</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>19</v>
@@ -7687,7 +8117,7 @@
         <v>395</v>
       </c>
       <c r="D129" t="s">
-        <v>396</v>
+        <v>584</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>19</v>
@@ -7707,7 +8137,7 @@
         <v>398</v>
       </c>
       <c r="D130" t="s">
-        <v>399</v>
+        <v>585</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>9</v>
@@ -7727,7 +8157,7 @@
         <v>401</v>
       </c>
       <c r="D131" t="s">
-        <v>402</v>
+        <v>586</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>113</v>
@@ -7747,7 +8177,7 @@
         <v>404</v>
       </c>
       <c r="D132" t="s">
-        <v>405</v>
+        <v>587</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>72</v>
@@ -7767,7 +8197,7 @@
         <v>407</v>
       </c>
       <c r="D133" t="s">
-        <v>408</v>
+        <v>588</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>14</v>
@@ -7787,7 +8217,7 @@
         <v>410</v>
       </c>
       <c r="D134" t="s">
-        <v>411</v>
+        <v>589</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>54</v>
@@ -7807,7 +8237,7 @@
         <v>419</v>
       </c>
       <c r="D135" t="s">
-        <v>420</v>
+        <v>590</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>68</v>
@@ -7827,7 +8257,7 @@
         <v>267</v>
       </c>
       <c r="D136" t="s">
-        <v>422</v>
+        <v>591</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>68</v>
@@ -7847,7 +8277,7 @@
         <v>424</v>
       </c>
       <c r="D137" t="s">
-        <v>425</v>
+        <v>592</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>68</v>
@@ -7867,7 +8297,7 @@
         <v>427</v>
       </c>
       <c r="D138" t="s">
-        <v>428</v>
+        <v>593</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>41</v>
@@ -7887,7 +8317,7 @@
         <v>430</v>
       </c>
       <c r="D139" t="s">
-        <v>431</v>
+        <v>594</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>19</v>
@@ -7907,7 +8337,7 @@
         <v>433</v>
       </c>
       <c r="D140" t="s">
-        <v>434</v>
+        <v>595</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>9</v>
@@ -7927,7 +8357,7 @@
         <v>436</v>
       </c>
       <c r="D141" t="s">
-        <v>437</v>
+        <v>596</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>41</v>
@@ -7947,7 +8377,7 @@
         <v>439</v>
       </c>
       <c r="D142" t="s">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>54</v>
@@ -8036,44 +8466,44 @@
         <v>4</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>5</v>
+        <v>597</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>1035</v>
+        <v>1112</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>296</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>297</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>551</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>1036</v>
+        <v>1160</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>365</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>297</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>574</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>10</v>
@@ -8081,19 +8511,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>1037</v>
+        <v>1096</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>284</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>285</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>547</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>15</v>
@@ -8101,99 +8531,97 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>462</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>453</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>1039</v>
+        <v>1142</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>409</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>410</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>589</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>1040</v>
+        <v>1079</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>473</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>10</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="F10" s="1"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>1042</v>
+        <v>1029</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>290</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>291</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>549</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>1044</v>
+        <v>1054</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>477</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>15</v>
@@ -8201,137 +8629,139 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>1045</v>
+        <v>1143</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>406</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>407</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
+        <v>588</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>1046</v>
+        <v>1053</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>476</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>1031</v>
+        <v>1077</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>263</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>264</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>540</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>15</v>
+        <v>454</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>1169</v>
+        <v>1041</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>218</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>219</v>
       </c>
       <c r="D16" t="s">
-        <v>50</v>
+        <v>525</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>455</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>1168</v>
+        <v>1045</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="D17" t="s">
-        <v>53</v>
+        <v>468</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>455</v>
+        <v>41</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>1079</v>
+        <v>1060</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>239</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>240</v>
       </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>532</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="G18" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>1048</v>
+        <v>1152</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>356</v>
       </c>
       <c r="C19" t="s">
-        <v>60</v>
+        <v>357</v>
       </c>
       <c r="D19" t="s">
-        <v>61</v>
+        <v>571</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>19</v>
@@ -8342,39 +8772,39 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>1050</v>
+        <v>1069</v>
       </c>
       <c r="B20" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="D20" t="s">
-        <v>64</v>
+        <v>485</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>1053</v>
+        <v>1158</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>373</v>
       </c>
       <c r="C21" t="s">
-        <v>66</v>
+        <v>374</v>
       </c>
       <c r="D21" t="s">
-        <v>67</v>
+        <v>577</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>47</v>
@@ -8382,19 +8812,19 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>1054</v>
+        <v>1101</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>152</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>153</v>
       </c>
       <c r="D22" t="s">
-        <v>71</v>
+        <v>503</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>15</v>
@@ -8402,19 +8832,19 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>1058</v>
+        <v>1103</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>155</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>156</v>
       </c>
       <c r="D23" t="s">
-        <v>75</v>
+        <v>504</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>15</v>
@@ -8422,36 +8852,36 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>242</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>243</v>
       </c>
       <c r="D24" t="s">
-        <v>79</v>
+        <v>533</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>1061</v>
+        <v>1056</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="C25" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="D25" t="s">
-        <v>82</v>
+        <v>494</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>19</v>
@@ -8462,39 +8892,39 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>1062</v>
+        <v>1071</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D26" t="s">
-        <v>85</v>
+        <v>486</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>1064</v>
+        <v>1030</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>257</v>
       </c>
       <c r="C27" t="s">
-        <v>87</v>
+        <v>258</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>538</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>15</v>
@@ -8502,16 +8932,16 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>1065</v>
+        <v>1075</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="C28" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="D28" t="s">
-        <v>91</v>
+        <v>488</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>19</v>
@@ -8522,139 +8952,139 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>1067</v>
+        <v>1038</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="C29" t="s">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="D29" t="s">
-        <v>94</v>
+        <v>463</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>1069</v>
+        <v>1148</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>397</v>
       </c>
       <c r="C30" t="s">
-        <v>96</v>
+        <v>398</v>
       </c>
       <c r="D30" t="s">
-        <v>97</v>
+        <v>585</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>1071</v>
+        <v>1131</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>317</v>
       </c>
       <c r="C31" t="s">
-        <v>99</v>
+        <v>318</v>
       </c>
       <c r="D31" t="s">
-        <v>100</v>
+        <v>558</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="B32" t="s">
-        <v>101</v>
+        <v>418</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
+        <v>419</v>
       </c>
       <c r="D32" t="s">
-        <v>103</v>
+        <v>590</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>1075</v>
+        <v>1121</v>
       </c>
       <c r="B33" t="s">
-        <v>104</v>
+        <v>350</v>
       </c>
       <c r="C33" t="s">
-        <v>105</v>
+        <v>351</v>
       </c>
       <c r="D33" t="s">
-        <v>106</v>
+        <v>569</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>1078</v>
+        <v>1032</v>
       </c>
       <c r="B34" t="s">
-        <v>107</v>
+        <v>335</v>
       </c>
       <c r="C34" t="s">
-        <v>108</v>
+        <v>336</v>
       </c>
       <c r="D34" t="s">
-        <v>109</v>
+        <v>564</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>15</v>
+        <v>453</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>1080</v>
+        <v>1129</v>
       </c>
       <c r="B35" t="s">
-        <v>110</v>
+        <v>308</v>
       </c>
       <c r="C35" t="s">
-        <v>111</v>
+        <v>309</v>
       </c>
       <c r="D35" t="s">
-        <v>112</v>
+        <v>555</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>113</v>
+        <v>26</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>15</v>
@@ -8662,19 +9092,19 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>1081</v>
+        <v>1130</v>
       </c>
       <c r="B36" t="s">
-        <v>114</v>
+        <v>215</v>
       </c>
       <c r="C36" t="s">
-        <v>115</v>
+        <v>216</v>
       </c>
       <c r="D36" t="s">
-        <v>116</v>
+        <v>524</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>15</v>
@@ -8682,19 +9112,19 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B37" t="s">
-        <v>117</v>
+        <v>266</v>
       </c>
       <c r="C37" t="s">
-        <v>118</v>
+        <v>267</v>
       </c>
       <c r="D37" t="s">
-        <v>119</v>
+        <v>541</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>15</v>
@@ -8702,182 +9132,182 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>1084</v>
+        <v>1102</v>
       </c>
       <c r="B38" t="s">
-        <v>120</v>
+        <v>421</v>
       </c>
       <c r="C38" t="s">
-        <v>121</v>
+        <v>267</v>
       </c>
       <c r="D38" t="s">
-        <v>122</v>
+        <v>591</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>47</v>
+        <v>452</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>1056</v>
+        <v>1116</v>
       </c>
       <c r="B39" t="s">
-        <v>123</v>
+        <v>299</v>
       </c>
       <c r="C39" t="s">
-        <v>124</v>
+        <v>300</v>
       </c>
       <c r="D39" t="s">
-        <v>125</v>
+        <v>552</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>15</v>
+        <v>453</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>1088</v>
+        <v>1115</v>
       </c>
       <c r="B40" t="s">
-        <v>126</v>
+        <v>182</v>
       </c>
       <c r="C40" t="s">
-        <v>127</v>
+        <v>183</v>
       </c>
       <c r="D40" t="s">
-        <v>128</v>
+        <v>513</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>1166</v>
+        <v>1091</v>
       </c>
       <c r="B41" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C41" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D41" t="s">
-        <v>131</v>
+        <v>497</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>1091</v>
+        <v>1100</v>
       </c>
       <c r="B42" t="s">
-        <v>132</v>
+        <v>230</v>
       </c>
       <c r="C42" t="s">
-        <v>133</v>
+        <v>231</v>
       </c>
       <c r="D42" t="s">
-        <v>134</v>
+        <v>529</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>9</v>
+        <v>151</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>1092</v>
+        <v>1150</v>
       </c>
       <c r="B43" t="s">
-        <v>135</v>
+        <v>388</v>
       </c>
       <c r="C43" t="s">
-        <v>136</v>
+        <v>389</v>
       </c>
       <c r="D43" t="s">
-        <v>137</v>
+        <v>582</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>68</v>
+        <v>113</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>47</v>
+        <v>453</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>1094</v>
+        <v>1136</v>
       </c>
       <c r="B44" t="s">
-        <v>138</v>
+        <v>332</v>
       </c>
       <c r="C44" t="s">
-        <v>139</v>
+        <v>333</v>
       </c>
       <c r="D44" t="s">
-        <v>140</v>
+        <v>563</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>443</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="B45" t="s">
-        <v>141</v>
+        <v>423</v>
       </c>
       <c r="C45" t="s">
-        <v>142</v>
+        <v>424</v>
       </c>
       <c r="D45" t="s">
-        <v>143</v>
+        <v>592</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>47</v>
+        <v>455</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>1098</v>
+        <v>1139</v>
       </c>
       <c r="B46" t="s">
-        <v>144</v>
+        <v>344</v>
       </c>
       <c r="C46" t="s">
-        <v>145</v>
+        <v>345</v>
       </c>
       <c r="D46" t="s">
-        <v>146</v>
+        <v>567</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>15</v>
+        <v>453</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -8891,7 +9321,7 @@
         <v>149</v>
       </c>
       <c r="D47" t="s">
-        <v>150</v>
+        <v>502</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>151</v>
@@ -8902,79 +9332,79 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="B48" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C48" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="D48" t="s">
-        <v>154</v>
+        <v>505</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>54</v>
+        <v>113</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>1103</v>
+        <v>1146</v>
       </c>
       <c r="B49" t="s">
-        <v>155</v>
+        <v>426</v>
       </c>
       <c r="C49" t="s">
-        <v>156</v>
+        <v>427</v>
       </c>
       <c r="D49" t="s">
-        <v>157</v>
+        <v>593</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>113</v>
+        <v>41</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>15</v>
+        <v>455</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>1104</v>
+        <v>1057</v>
       </c>
       <c r="B50" t="s">
-        <v>158</v>
+        <v>236</v>
       </c>
       <c r="C50" t="s">
-        <v>159</v>
+        <v>237</v>
       </c>
       <c r="D50" t="s">
-        <v>160</v>
+        <v>531</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>113</v>
+        <v>29</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>1105</v>
+        <v>1122</v>
       </c>
       <c r="B51" t="s">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="C51" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="D51" t="s">
-        <v>163</v>
+        <v>517</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>15</v>
@@ -8982,62 +9412,62 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>1106</v>
+        <v>1128</v>
       </c>
       <c r="B52" t="s">
-        <v>164</v>
+        <v>212</v>
       </c>
       <c r="C52" t="s">
-        <v>165</v>
+        <v>213</v>
       </c>
       <c r="D52" t="s">
-        <v>166</v>
+        <v>523</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>15</v>
+        <v>453</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>1107</v>
+        <v>1044</v>
       </c>
       <c r="B53" t="s">
-        <v>167</v>
+        <v>34</v>
       </c>
       <c r="C53" t="s">
-        <v>168</v>
+        <v>35</v>
       </c>
       <c r="D53" t="s">
-        <v>169</v>
+        <v>467</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>443</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>1110</v>
+        <v>1149</v>
       </c>
       <c r="B54" t="s">
-        <v>170</v>
+        <v>391</v>
       </c>
       <c r="C54" t="s">
-        <v>171</v>
+        <v>392</v>
       </c>
       <c r="D54" t="s">
-        <v>172</v>
+        <v>583</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -9051,7 +9481,7 @@
         <v>174</v>
       </c>
       <c r="D55" t="s">
-        <v>175</v>
+        <v>510</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>29</v>
@@ -9062,79 +9492,79 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>1114</v>
+        <v>1031</v>
       </c>
       <c r="B56" t="s">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="C56" t="s">
-        <v>177</v>
+        <v>45</v>
       </c>
       <c r="D56" t="s">
-        <v>178</v>
+        <v>470</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>441</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>1165</v>
+        <v>1067</v>
       </c>
       <c r="B57" t="s">
-        <v>179</v>
+        <v>92</v>
       </c>
       <c r="C57" t="s">
-        <v>180</v>
+        <v>93</v>
       </c>
       <c r="D57" t="s">
-        <v>181</v>
+        <v>484</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>15</v>
+        <v>454</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>1115</v>
+        <v>1108</v>
       </c>
       <c r="B58" t="s">
-        <v>182</v>
+        <v>429</v>
       </c>
       <c r="C58" t="s">
-        <v>183</v>
+        <v>430</v>
       </c>
       <c r="D58" t="s">
-        <v>184</v>
+        <v>594</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>47</v>
+        <v>455</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>1117</v>
+        <v>1137</v>
       </c>
       <c r="B59" t="s">
-        <v>185</v>
+        <v>338</v>
       </c>
       <c r="C59" t="s">
-        <v>186</v>
+        <v>339</v>
       </c>
       <c r="D59" t="s">
-        <v>187</v>
+        <v>565</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>15</v>
@@ -9142,59 +9572,59 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>1119</v>
+        <v>1163</v>
       </c>
       <c r="B60" t="s">
-        <v>188</v>
+        <v>311</v>
       </c>
       <c r="C60" t="s">
-        <v>189</v>
+        <v>312</v>
       </c>
       <c r="D60" t="s">
-        <v>190</v>
+        <v>556</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>151</v>
+        <v>29</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>453</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>1120</v>
+        <v>1089</v>
       </c>
       <c r="B61" t="s">
-        <v>191</v>
+        <v>432</v>
       </c>
       <c r="C61" t="s">
-        <v>192</v>
+        <v>433</v>
       </c>
       <c r="D61" t="s">
-        <v>193</v>
+        <v>595</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>15</v>
+        <v>455</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>1122</v>
+        <v>1133</v>
       </c>
       <c r="B62" t="s">
-        <v>194</v>
+        <v>323</v>
       </c>
       <c r="C62" t="s">
-        <v>195</v>
+        <v>324</v>
       </c>
       <c r="D62" t="s">
-        <v>196</v>
+        <v>560</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>15</v>
@@ -9202,19 +9632,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>1123</v>
+        <v>1140</v>
       </c>
       <c r="B63" t="s">
-        <v>197</v>
+        <v>347</v>
       </c>
       <c r="C63" t="s">
-        <v>198</v>
+        <v>348</v>
       </c>
       <c r="D63" t="s">
-        <v>199</v>
+        <v>568</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>15</v>
@@ -9222,19 +9652,19 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>1124</v>
+        <v>1052</v>
       </c>
       <c r="B64" t="s">
-        <v>200</v>
+        <v>305</v>
       </c>
       <c r="C64" t="s">
-        <v>201</v>
+        <v>306</v>
       </c>
       <c r="D64" t="s">
-        <v>202</v>
+        <v>554</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>15</v>
@@ -9242,19 +9672,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>1125</v>
+        <v>1099</v>
       </c>
       <c r="B65" t="s">
-        <v>203</v>
+        <v>287</v>
       </c>
       <c r="C65" t="s">
-        <v>204</v>
+        <v>288</v>
       </c>
       <c r="D65" t="s">
-        <v>205</v>
+        <v>548</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>15</v>
@@ -9262,99 +9692,99 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>1126</v>
+        <v>1049</v>
       </c>
       <c r="B66" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="C66" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="D66" t="s">
-        <v>208</v>
+        <v>528</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>15</v>
+        <v>454</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>1127</v>
+        <v>1065</v>
       </c>
       <c r="B67" t="s">
-        <v>209</v>
+        <v>89</v>
       </c>
       <c r="C67" t="s">
-        <v>210</v>
+        <v>90</v>
       </c>
       <c r="D67" t="s">
-        <v>211</v>
+        <v>483</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>151</v>
+        <v>19</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>1128</v>
+        <v>1107</v>
       </c>
       <c r="B68" t="s">
-        <v>212</v>
+        <v>167</v>
       </c>
       <c r="C68" t="s">
-        <v>213</v>
+        <v>168</v>
       </c>
       <c r="D68" t="s">
-        <v>214</v>
+        <v>508</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>1130</v>
+        <v>1059</v>
       </c>
       <c r="B69" t="s">
-        <v>215</v>
+        <v>77</v>
       </c>
       <c r="C69" t="s">
-        <v>216</v>
+        <v>78</v>
       </c>
       <c r="D69" t="s">
-        <v>217</v>
+        <v>479</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>1041</v>
+        <v>1083</v>
       </c>
       <c r="B70" t="s">
-        <v>218</v>
+        <v>117</v>
       </c>
       <c r="C70" t="s">
-        <v>219</v>
+        <v>118</v>
       </c>
       <c r="D70" t="s">
-        <v>220</v>
+        <v>492</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>15</v>
@@ -9362,19 +9792,19 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>1164</v>
+        <v>1087</v>
       </c>
       <c r="B71" t="s">
-        <v>221</v>
+        <v>272</v>
       </c>
       <c r="C71" t="s">
-        <v>222</v>
+        <v>273</v>
       </c>
       <c r="D71" t="s">
-        <v>223</v>
+        <v>543</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>15</v>
@@ -9382,99 +9812,99 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>1043</v>
+        <v>1162</v>
       </c>
       <c r="B72" t="s">
-        <v>224</v>
+        <v>314</v>
       </c>
       <c r="C72" t="s">
-        <v>225</v>
+        <v>315</v>
       </c>
       <c r="D72" t="s">
-        <v>226</v>
+        <v>557</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>14</v>
+        <v>113</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>47</v>
+        <v>441</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>1049</v>
+        <v>1066</v>
       </c>
       <c r="B73" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="C73" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="D73" t="s">
-        <v>229</v>
+        <v>534</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>454</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>1100</v>
+        <v>1120</v>
       </c>
       <c r="B74" t="s">
-        <v>230</v>
+        <v>191</v>
       </c>
       <c r="C74" t="s">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="D74" t="s">
-        <v>232</v>
+        <v>516</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>151</v>
+        <v>19</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>1055</v>
+        <v>1114</v>
       </c>
       <c r="B75" t="s">
-        <v>233</v>
+        <v>176</v>
       </c>
       <c r="C75" t="s">
-        <v>234</v>
+        <v>177</v>
       </c>
       <c r="D75" t="s">
-        <v>235</v>
+        <v>511</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>15</v>
+        <v>441</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="B76" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C76" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D76" t="s">
-        <v>238</v>
+        <v>530</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>15</v>
@@ -9482,56 +9912,56 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>1060</v>
+        <v>1157</v>
       </c>
       <c r="B77" t="s">
-        <v>239</v>
+        <v>362</v>
       </c>
       <c r="C77" t="s">
-        <v>240</v>
+        <v>363</v>
       </c>
       <c r="D77" t="s">
-        <v>241</v>
+        <v>573</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>1063</v>
+        <v>1097</v>
       </c>
       <c r="B78" t="s">
-        <v>242</v>
+        <v>141</v>
       </c>
       <c r="C78" t="s">
-        <v>243</v>
+        <v>142</v>
       </c>
       <c r="D78" t="s">
-        <v>244</v>
+        <v>500</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>1066</v>
+        <v>1125</v>
       </c>
       <c r="B79" t="s">
-        <v>245</v>
+        <v>203</v>
       </c>
       <c r="C79" t="s">
-        <v>246</v>
+        <v>204</v>
       </c>
       <c r="D79" t="s">
-        <v>247</v>
+        <v>520</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>29</v>
@@ -9542,59 +9972,59 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>1068</v>
+        <v>1138</v>
       </c>
       <c r="B80" t="s">
-        <v>248</v>
+        <v>341</v>
       </c>
       <c r="C80" t="s">
-        <v>249</v>
+        <v>342</v>
       </c>
       <c r="D80" t="s">
-        <v>250</v>
+        <v>566</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>443</v>
+        <v>15</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>1070</v>
+        <v>1081</v>
       </c>
       <c r="B81" t="s">
-        <v>251</v>
+        <v>114</v>
       </c>
       <c r="C81" t="s">
-        <v>252</v>
+        <v>115</v>
       </c>
       <c r="D81" t="s">
-        <v>253</v>
+        <v>491</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>453</v>
+        <v>15</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>1072</v>
+        <v>1088</v>
       </c>
       <c r="B82" t="s">
-        <v>254</v>
+        <v>126</v>
       </c>
       <c r="C82" t="s">
-        <v>255</v>
+        <v>127</v>
       </c>
       <c r="D82" t="s">
-        <v>256</v>
+        <v>495</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>15</v>
@@ -9602,19 +10032,19 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>1030</v>
+        <v>1165</v>
       </c>
       <c r="B83" t="s">
-        <v>257</v>
+        <v>179</v>
       </c>
       <c r="C83" t="s">
-        <v>258</v>
+        <v>180</v>
       </c>
       <c r="D83" t="s">
-        <v>259</v>
+        <v>512</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>15</v>
@@ -9622,19 +10052,19 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>1076</v>
+        <v>1159</v>
       </c>
       <c r="B84" t="s">
-        <v>260</v>
+        <v>370</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>371</v>
       </c>
       <c r="D84" t="s">
-        <v>262</v>
+        <v>576</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>15</v>
@@ -9642,59 +10072,59 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>1077</v>
+        <v>1154</v>
       </c>
       <c r="B85" t="s">
-        <v>263</v>
+        <v>379</v>
       </c>
       <c r="C85" t="s">
-        <v>264</v>
+        <v>380</v>
       </c>
       <c r="D85" t="s">
-        <v>265</v>
+        <v>579</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>72</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>454</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>1082</v>
+        <v>1127</v>
       </c>
       <c r="B86" t="s">
-        <v>266</v>
+        <v>209</v>
       </c>
       <c r="C86" t="s">
-        <v>267</v>
+        <v>210</v>
       </c>
       <c r="D86" t="s">
-        <v>268</v>
+        <v>522</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>41</v>
+        <v>151</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>1085</v>
+        <v>1124</v>
       </c>
       <c r="B87" t="s">
-        <v>269</v>
+        <v>200</v>
       </c>
       <c r="C87" t="s">
-        <v>270</v>
+        <v>201</v>
       </c>
       <c r="D87" t="s">
-        <v>271</v>
+        <v>519</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>15</v>
@@ -9702,99 +10132,99 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>1087</v>
+        <v>1068</v>
       </c>
       <c r="B88" t="s">
-        <v>272</v>
+        <v>248</v>
       </c>
       <c r="C88" t="s">
-        <v>273</v>
+        <v>249</v>
       </c>
       <c r="D88" t="s">
-        <v>274</v>
+        <v>535</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>15</v>
+        <v>443</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>1167</v>
+        <v>1118</v>
       </c>
       <c r="B89" t="s">
-        <v>275</v>
+        <v>302</v>
       </c>
       <c r="C89" t="s">
-        <v>276</v>
+        <v>303</v>
       </c>
       <c r="D89" t="s">
-        <v>277</v>
+        <v>553</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>455</v>
+        <v>15</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>1090</v>
+        <v>1039</v>
       </c>
       <c r="B90" t="s">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="C90" t="s">
-        <v>279</v>
+        <v>24</v>
       </c>
       <c r="D90" t="s">
-        <v>280</v>
+        <v>464</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>454</v>
+        <v>15</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>1093</v>
+        <v>1048</v>
       </c>
       <c r="B91" t="s">
-        <v>281</v>
+        <v>59</v>
       </c>
       <c r="C91" t="s">
-        <v>282</v>
+        <v>60</v>
       </c>
       <c r="D91" t="s">
-        <v>283</v>
+        <v>474</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>1096</v>
+        <v>1074</v>
       </c>
       <c r="B92" t="s">
-        <v>284</v>
+        <v>394</v>
       </c>
       <c r="C92" t="s">
-        <v>285</v>
+        <v>395</v>
       </c>
       <c r="D92" t="s">
-        <v>286</v>
+        <v>584</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>15</v>
@@ -9802,36 +10232,36 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>1099</v>
+        <v>1168</v>
       </c>
       <c r="B93" t="s">
-        <v>287</v>
+        <v>51</v>
       </c>
       <c r="C93" t="s">
-        <v>288</v>
+        <v>52</v>
       </c>
       <c r="D93" t="s">
-        <v>289</v>
+        <v>472</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>15</v>
+        <v>54</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>1029</v>
+        <v>1092</v>
       </c>
       <c r="B94" t="s">
-        <v>290</v>
+        <v>135</v>
       </c>
       <c r="C94" t="s">
-        <v>291</v>
+        <v>136</v>
       </c>
       <c r="D94" t="s">
-        <v>292</v>
+        <v>498</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>68</v>
@@ -9842,99 +10272,99 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>1109</v>
+        <v>1119</v>
       </c>
       <c r="B95" t="s">
-        <v>293</v>
+        <v>188</v>
       </c>
       <c r="C95" t="s">
-        <v>294</v>
+        <v>189</v>
       </c>
       <c r="D95" t="s">
-        <v>295</v>
+        <v>515</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>9</v>
+        <v>151</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>1112</v>
+        <v>1093</v>
       </c>
       <c r="B96" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="C96" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="D96" t="s">
-        <v>298</v>
+        <v>546</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>1116</v>
+        <v>1094</v>
       </c>
       <c r="B97" t="s">
-        <v>299</v>
+        <v>138</v>
       </c>
       <c r="C97" t="s">
-        <v>300</v>
+        <v>139</v>
       </c>
       <c r="D97" t="s">
-        <v>301</v>
+        <v>499</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>1118</v>
+        <v>1070</v>
       </c>
       <c r="B98" t="s">
-        <v>302</v>
+        <v>251</v>
       </c>
       <c r="C98" t="s">
-        <v>303</v>
+        <v>252</v>
       </c>
       <c r="D98" t="s">
-        <v>304</v>
+        <v>536</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>15</v>
+        <v>453</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>1052</v>
+        <v>1042</v>
       </c>
       <c r="B99" t="s">
-        <v>305</v>
+        <v>30</v>
       </c>
       <c r="C99" t="s">
-        <v>306</v>
+        <v>31</v>
       </c>
       <c r="D99" t="s">
-        <v>307</v>
+        <v>466</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>15</v>
@@ -9942,39 +10372,39 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>1129</v>
+        <v>1153</v>
       </c>
       <c r="B100" t="s">
-        <v>308</v>
+        <v>382</v>
       </c>
       <c r="C100" t="s">
-        <v>309</v>
+        <v>383</v>
       </c>
       <c r="D100" t="s">
-        <v>310</v>
+        <v>580</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>15</v>
+        <v>444</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>1163</v>
+        <v>1046</v>
       </c>
       <c r="B101" t="s">
-        <v>311</v>
+        <v>38</v>
       </c>
       <c r="C101" t="s">
-        <v>312</v>
+        <v>42</v>
       </c>
       <c r="D101" t="s">
-        <v>313</v>
+        <v>469</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>15</v>
@@ -9982,39 +10412,39 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="B102" t="s">
-        <v>314</v>
+        <v>221</v>
       </c>
       <c r="C102" t="s">
-        <v>315</v>
+        <v>222</v>
       </c>
       <c r="D102" t="s">
-        <v>316</v>
+        <v>526</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>113</v>
+        <v>41</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>441</v>
+        <v>15</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103">
-        <v>1131</v>
+        <v>1085</v>
       </c>
       <c r="B103" t="s">
-        <v>317</v>
+        <v>269</v>
       </c>
       <c r="C103" t="s">
-        <v>318</v>
+        <v>270</v>
       </c>
       <c r="D103" t="s">
-        <v>319</v>
+        <v>542</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>15</v>
@@ -10022,79 +10452,79 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>1132</v>
+        <v>1072</v>
       </c>
       <c r="B104" t="s">
-        <v>320</v>
+        <v>254</v>
       </c>
       <c r="C104" t="s">
-        <v>321</v>
+        <v>255</v>
       </c>
       <c r="D104" t="s">
-        <v>322</v>
+        <v>537</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>444</v>
+        <v>15</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>1133</v>
+        <v>1110</v>
       </c>
       <c r="B105" t="s">
-        <v>323</v>
+        <v>170</v>
       </c>
       <c r="C105" t="s">
-        <v>324</v>
+        <v>171</v>
       </c>
       <c r="D105" t="s">
-        <v>325</v>
+        <v>509</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106">
-        <v>1134</v>
+        <v>1141</v>
       </c>
       <c r="B106" t="s">
-        <v>326</v>
+        <v>367</v>
       </c>
       <c r="C106" t="s">
-        <v>327</v>
+        <v>368</v>
       </c>
       <c r="D106" t="s">
-        <v>328</v>
+        <v>575</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>453</v>
+        <v>15</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107">
-        <v>1135</v>
+        <v>1145</v>
       </c>
       <c r="B107" t="s">
-        <v>329</v>
+        <v>400</v>
       </c>
       <c r="C107" t="s">
-        <v>330</v>
+        <v>401</v>
       </c>
       <c r="D107" t="s">
-        <v>331</v>
+        <v>586</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>15</v>
@@ -10102,16 +10532,16 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>1136</v>
+        <v>1050</v>
       </c>
       <c r="B108" t="s">
-        <v>332</v>
+        <v>62</v>
       </c>
       <c r="C108" t="s">
-        <v>333</v>
+        <v>63</v>
       </c>
       <c r="D108" t="s">
-        <v>334</v>
+        <v>475</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>37</v>
@@ -10122,39 +10552,39 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>1032</v>
+        <v>1151</v>
       </c>
       <c r="B109" t="s">
-        <v>335</v>
+        <v>385</v>
       </c>
       <c r="C109" t="s">
-        <v>336</v>
+        <v>386</v>
       </c>
       <c r="D109" t="s">
-        <v>337</v>
+        <v>581</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>453</v>
+        <v>15</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110">
-        <v>1137</v>
+        <v>1061</v>
       </c>
       <c r="B110" t="s">
-        <v>338</v>
+        <v>80</v>
       </c>
       <c r="C110" t="s">
-        <v>339</v>
+        <v>81</v>
       </c>
       <c r="D110" t="s">
-        <v>340</v>
+        <v>480</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>15</v>
@@ -10162,39 +10592,39 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111">
-        <v>1138</v>
+        <v>1035</v>
       </c>
       <c r="B111" t="s">
-        <v>341</v>
+        <v>6</v>
       </c>
       <c r="C111" t="s">
-        <v>342</v>
+        <v>7</v>
       </c>
       <c r="D111" t="s">
-        <v>343</v>
+        <v>459</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112">
-        <v>1139</v>
+        <v>1047</v>
       </c>
       <c r="B112" t="s">
-        <v>344</v>
+        <v>101</v>
       </c>
       <c r="C112" t="s">
-        <v>345</v>
+        <v>102</v>
       </c>
       <c r="D112" t="s">
-        <v>346</v>
+        <v>487</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>453</v>
@@ -10202,19 +10632,19 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113">
-        <v>1140</v>
+        <v>1117</v>
       </c>
       <c r="B113" t="s">
-        <v>347</v>
+        <v>185</v>
       </c>
       <c r="C113" t="s">
-        <v>348</v>
+        <v>186</v>
       </c>
       <c r="D113" t="s">
-        <v>349</v>
+        <v>514</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>15</v>
@@ -10222,79 +10652,79 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114">
-        <v>1121</v>
+        <v>1156</v>
       </c>
       <c r="B114" t="s">
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="C114" t="s">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="D114" t="s">
-        <v>352</v>
+        <v>578</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115">
-        <v>1147</v>
+        <v>1166</v>
       </c>
       <c r="B115" t="s">
-        <v>353</v>
+        <v>129</v>
       </c>
       <c r="C115" t="s">
-        <v>354</v>
+        <v>130</v>
       </c>
       <c r="D115" t="s">
-        <v>355</v>
+        <v>496</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116">
-        <v>1152</v>
+        <v>1090</v>
       </c>
       <c r="B116" t="s">
-        <v>356</v>
+        <v>278</v>
       </c>
       <c r="C116" t="s">
-        <v>357</v>
+        <v>279</v>
       </c>
       <c r="D116" t="s">
-        <v>358</v>
+        <v>545</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>15</v>
+        <v>454</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117">
-        <v>1155</v>
+        <v>1111</v>
       </c>
       <c r="B117" t="s">
-        <v>359</v>
+        <v>435</v>
       </c>
       <c r="C117" t="s">
-        <v>360</v>
+        <v>436</v>
       </c>
       <c r="D117" t="s">
-        <v>361</v>
+        <v>596</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>15</v>
@@ -10302,79 +10732,79 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118">
-        <v>1157</v>
+        <v>1078</v>
       </c>
       <c r="B118" t="s">
-        <v>362</v>
+        <v>107</v>
       </c>
       <c r="C118" t="s">
-        <v>363</v>
+        <v>108</v>
       </c>
       <c r="D118" t="s">
-        <v>364</v>
+        <v>489</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119">
-        <v>1160</v>
+        <v>1147</v>
       </c>
       <c r="B119" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="C119" t="s">
-        <v>297</v>
+        <v>354</v>
       </c>
       <c r="D119" t="s">
-        <v>366</v>
+        <v>570</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>68</v>
+        <v>113</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120">
-        <v>1141</v>
+        <v>1167</v>
       </c>
       <c r="B120" t="s">
-        <v>367</v>
+        <v>275</v>
       </c>
       <c r="C120" t="s">
-        <v>368</v>
+        <v>276</v>
       </c>
       <c r="D120" t="s">
-        <v>369</v>
+        <v>544</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>15</v>
+        <v>455</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121">
-        <v>1159</v>
+        <v>1144</v>
       </c>
       <c r="B121" t="s">
-        <v>370</v>
+        <v>403</v>
       </c>
       <c r="C121" t="s">
-        <v>371</v>
+        <v>404</v>
       </c>
       <c r="D121" t="s">
-        <v>372</v>
+        <v>587</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>15</v>
@@ -10382,39 +10812,39 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122">
-        <v>1158</v>
+        <v>1040</v>
       </c>
       <c r="B122" t="s">
-        <v>373</v>
+        <v>23</v>
       </c>
       <c r="C122" t="s">
-        <v>374</v>
+        <v>27</v>
       </c>
       <c r="D122" t="s">
-        <v>375</v>
+        <v>465</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123">
-        <v>1156</v>
+        <v>1098</v>
       </c>
       <c r="B123" t="s">
-        <v>376</v>
+        <v>144</v>
       </c>
       <c r="C123" t="s">
-        <v>377</v>
+        <v>145</v>
       </c>
       <c r="D123" t="s">
-        <v>378</v>
+        <v>501</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>15</v>
@@ -10422,39 +10852,39 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124">
-        <v>1154</v>
+        <v>1109</v>
       </c>
       <c r="B124" t="s">
-        <v>379</v>
+        <v>293</v>
       </c>
       <c r="C124" t="s">
-        <v>380</v>
+        <v>294</v>
       </c>
       <c r="D124" t="s">
-        <v>381</v>
+        <v>550</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>15</v>
+        <v>441</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125">
-        <v>1153</v>
+        <v>1132</v>
       </c>
       <c r="B125" t="s">
-        <v>382</v>
+        <v>320</v>
       </c>
       <c r="C125" t="s">
-        <v>383</v>
+        <v>321</v>
       </c>
       <c r="D125" t="s">
-        <v>384</v>
+        <v>559</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>444</v>
@@ -10462,19 +10892,19 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126">
-        <v>1151</v>
+        <v>1155</v>
       </c>
       <c r="B126" t="s">
-        <v>385</v>
+        <v>359</v>
       </c>
       <c r="C126" t="s">
-        <v>386</v>
+        <v>360</v>
       </c>
       <c r="D126" t="s">
-        <v>387</v>
+        <v>572</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>15</v>
@@ -10482,59 +10912,59 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127">
-        <v>1150</v>
+        <v>1062</v>
       </c>
       <c r="B127" t="s">
-        <v>388</v>
+        <v>83</v>
       </c>
       <c r="C127" t="s">
-        <v>389</v>
+        <v>84</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>481</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>113</v>
+        <v>26</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>453</v>
+        <v>15</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128">
-        <v>1149</v>
+        <v>1036</v>
       </c>
       <c r="B128" t="s">
-        <v>391</v>
+        <v>11</v>
       </c>
       <c r="C128" t="s">
-        <v>392</v>
+        <v>12</v>
       </c>
       <c r="D128" t="s">
-        <v>393</v>
+        <v>461</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129">
-        <v>1074</v>
+        <v>1123</v>
       </c>
       <c r="B129" t="s">
-        <v>394</v>
+        <v>197</v>
       </c>
       <c r="C129" t="s">
-        <v>395</v>
+        <v>198</v>
       </c>
       <c r="D129" t="s">
-        <v>396</v>
+        <v>518</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>15</v>
@@ -10542,19 +10972,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130">
-        <v>1148</v>
+        <v>1106</v>
       </c>
       <c r="B130" t="s">
-        <v>397</v>
+        <v>164</v>
       </c>
       <c r="C130" t="s">
-        <v>398</v>
+        <v>165</v>
       </c>
       <c r="D130" t="s">
-        <v>399</v>
+        <v>507</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>15</v>
@@ -10562,16 +10992,16 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131">
-        <v>1145</v>
+        <v>1080</v>
       </c>
       <c r="B131" t="s">
-        <v>400</v>
+        <v>110</v>
       </c>
       <c r="C131" t="s">
-        <v>401</v>
+        <v>111</v>
       </c>
       <c r="D131" t="s">
-        <v>402</v>
+        <v>490</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>113</v>
@@ -10582,19 +11012,19 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132">
-        <v>1144</v>
+        <v>1076</v>
       </c>
       <c r="B132" t="s">
-        <v>403</v>
+        <v>260</v>
       </c>
       <c r="C132" t="s">
-        <v>404</v>
+        <v>261</v>
       </c>
       <c r="D132" t="s">
-        <v>405</v>
+        <v>539</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>15</v>
@@ -10602,39 +11032,39 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133">
-        <v>1143</v>
+        <v>1105</v>
       </c>
       <c r="B133" t="s">
-        <v>406</v>
+        <v>161</v>
       </c>
       <c r="C133" t="s">
-        <v>407</v>
+        <v>162</v>
       </c>
       <c r="D133" t="s">
-        <v>408</v>
+        <v>506</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134">
-        <v>1142</v>
+        <v>1084</v>
       </c>
       <c r="B134" t="s">
-        <v>409</v>
+        <v>120</v>
       </c>
       <c r="C134" t="s">
-        <v>410</v>
+        <v>121</v>
       </c>
       <c r="D134" t="s">
-        <v>411</v>
+        <v>493</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>47</v>
@@ -10642,166 +11072,170 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135">
-        <v>1051</v>
+        <v>1043</v>
       </c>
       <c r="B135" t="s">
-        <v>418</v>
+        <v>224</v>
       </c>
       <c r="C135" t="s">
-        <v>419</v>
+        <v>225</v>
       </c>
       <c r="D135" t="s">
-        <v>420</v>
+        <v>527</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>455</v>
+        <v>47</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136">
-        <v>1102</v>
+        <v>1086</v>
       </c>
       <c r="B136" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="C136" t="s">
-        <v>267</v>
+        <v>439</v>
       </c>
       <c r="D136" t="s">
-        <v>422</v>
+        <v>460</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>452</v>
+        <v>10</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137">
-        <v>1095</v>
+        <v>1134</v>
       </c>
       <c r="B137" t="s">
-        <v>423</v>
+        <v>326</v>
       </c>
       <c r="C137" t="s">
-        <v>424</v>
+        <v>327</v>
       </c>
       <c r="D137" t="s">
-        <v>425</v>
+        <v>561</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138">
-        <v>1146</v>
+        <v>1135</v>
       </c>
       <c r="B138" t="s">
-        <v>426</v>
+        <v>329</v>
       </c>
       <c r="C138" t="s">
-        <v>427</v>
+        <v>330</v>
       </c>
       <c r="D138" t="s">
-        <v>428</v>
+        <v>562</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>455</v>
+        <v>15</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139">
-        <v>1108</v>
+        <v>1126</v>
       </c>
       <c r="B139" t="s">
-        <v>429</v>
+        <v>206</v>
       </c>
       <c r="C139" t="s">
-        <v>430</v>
+        <v>207</v>
       </c>
       <c r="D139" t="s">
-        <v>431</v>
+        <v>521</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>455</v>
+        <v>15</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140">
-        <v>1089</v>
+        <v>1058</v>
       </c>
       <c r="B140" t="s">
-        <v>432</v>
+        <v>73</v>
       </c>
       <c r="C140" t="s">
-        <v>433</v>
+        <v>74</v>
       </c>
       <c r="D140" t="s">
-        <v>434</v>
+        <v>478</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>455</v>
+        <v>15</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141">
-        <v>1111</v>
+        <v>1169</v>
       </c>
       <c r="B141" t="s">
-        <v>435</v>
+        <v>48</v>
       </c>
       <c r="C141" t="s">
-        <v>436</v>
+        <v>49</v>
       </c>
       <c r="D141" t="s">
-        <v>437</v>
+        <v>471</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>15</v>
+        <v>455</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142">
-        <v>1086</v>
+        <v>1064</v>
       </c>
       <c r="B142" t="s">
-        <v>438</v>
+        <v>86</v>
       </c>
       <c r="C142" t="s">
-        <v>439</v>
+        <v>87</v>
       </c>
       <c r="D142" t="s">
-        <v>440</v>
+        <v>482</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F142" xr:uid="{396C5EDA-B511-43A5-BE7B-39BAE596A57F}"/>
+  <autoFilter ref="A4:F142" xr:uid="{396C5EDA-B511-43A5-BE7B-39BAE596A57F}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:F142">
+      <sortCondition ref="C4:C142"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <extLst>
